--- a/input.xlsx
+++ b/input.xlsx
@@ -1,209 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="13320"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="26860" windowHeight="13320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>ASIN</t>
-  </si>
-  <si>
-    <t>B003G2ZKRC</t>
-  </si>
-  <si>
-    <t>B07SHFPD8S</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -503,160 +471,160 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -904,7 +872,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -913,7 +881,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -926,11 +894,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1182,34 +1213,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col width="15" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Bullet Points</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Details JSON</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>1</v>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>B003G2ZKRC</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>B003G2ZKRC</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>ORE International Six Foot Wood and Chrome Coat Rack Oak Finish</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>148.19</v>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>276</v>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Weago1KdL._AC_SL1500_.jpg</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>Coat Rack; Perfect for Keeping Hats and Coats Off the Floor
+12 Hooks Made of Chrome and Wood in Oak finish
+Unique fine moldings and classic turnings
+Oak and chrome coat rack with an elegant and casual design
+Unique fine mouldings and classic wood turnings
+12 chrome and wood hooks
+Practical and decorative
+Stands six feet tall</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>{"ASIN": "B003G2ZKRC", "Assembly Instructions Description": "Assembly Required", "Assembly Required": "Yes", "Batteries required": "No", "Best Sellers Rank": "#3,631,965 in Home &amp; Kitchen ( See Top 100 in Home &amp; Kitchen ) #1,223 in Coat Racks", "Brand": "ORE", "Color": "Brown", "Customer Reviews": "4.4 4.4 out of 5 stars 276 ratings 4.4 out of 5 stars", "Finish Type": "Wood", "Finish types": "Wood", "Frame Material": "Wood", "Furniture Finish": "Oak", "Global Trade Identification Number": "00075821458170", "Installation Type": "Free Standing", "Is Discontinued By Manufacturer": "No", "Item Weight": "0.01 Ounces", "Item model number": "R685OAK", "Load Capacity": "350 Pounds", "Manufacturer": "Ore International", "Material": "Wood", "Maximum Weight Recommendation": "350 Pounds", "Product Dimensions": "19 x 73 x 19 inches", "Recommended Uses For Product": "Coats", "Special Feature": "Elegant design", "Style": "Casual,Classic,Elegant", "UPC": "075821458170 882726288203", "Warranty Description": "60 days."}</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>2</v>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>B07SHFPD8S</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>B07SHFPD8S</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Pipishell Full Motion TV Wall Mount for Echo Show 21/15 and 13-42 Inch Flat Curved Screen TVs &amp; Monitors, Max VESA 200x200mm up to 44lbs, TV Mount Wall Bracket with Rotation Swivel Tilt Extension</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>133273</v>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61EBlj11AbL._AC_SL1500_.jpg</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>TV Mount Compatibility - The swivel TV wall mount is compatible with most LED LCD flat or curved 13″-42″ TVs/Monitors up to 44 lbs with VESA mounting patterns 75x75 to 200x200mm. The single TV mount can be installed on single wood studs, concrete, or brick walls, perfectly compatible with SAMSUNG, SONY, LG, VIZIO, TCL, ELEMENT, SCEPTRE, HISENSE and other TV brands. Please confirm your screen size and TV/monitor VESA before ordering.
+Full Motion for Optimal Viewing - Our articulating arm mount tilts +9°/-11° for anti-glaring, max swivels 90° display left or right according to your seats position (note: max. swivel angle depends on screen size) and rotates 360° for landscape and portrait orientation. It extends 14.59" and retracts back to 2.7" to save space. Makes your viewing or working feel more enjoyable!
+Universal Monitor Wall Mount - ideal for large computer monitors, especially monitors sizes 13, 17, 19, 21, 24, 27, 32, 34, 35 inch ultrawide monitors with VESA patterns from 75x75mm to 200x200mm. Use it as a full motion monitor wall mount to clear up desktop space and for ergonomic computer screen installation to improve your posture.
+Easy Installation - step-by-step instructions and all the necessary hardware is provided, single stud installation simplifies the placement of the TV/monitor on the wall. Removable TV plate designed for single-person installation which helps you to install this TV wall mount without any hassle.
+Friendly After-sales Service - our corner tv wall mount is constructed from high quality steel materials, we are so confident in the construction, strength and durability of this wall bracket that we are provide 5-year friendly customer service. Please feel free to contact us anytime, rain or shine:-)</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>{"ASIN": "B07SHFPD8S", "Best Sellers Rank": "#89 in Electronics ( See Top 100 in Electronics ) #4 in TV Wall &amp; Ceiling Mounts", "Brand Name": "‎Pipishell", "Color Name": "‎Black", "Customer Reviews": "4.6 4.6 out of 5 stars 133,273 ratings 4.6 out of 5 stars", "Date First Available": "May 31, 2019", "Item Weight": "‎2.7 pounds", "Item model number": "‎PISF1", "Product Dimensions": "‎9.61 x 6.22 x 2.4 inches", "Special Features": "‎Articulating/Full motion/swivel/tilt/wider rotation/low profile/extension"}</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="2"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/input.xlsx
+++ b/input.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="26860" windowHeight="13320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18060" windowHeight="7440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1292,31 +1292,26 @@
           <t>B003G2ZKRC</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>ORE International Six Foot Wood and Chrome Coat Rack Oak Finish</t>
         </is>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>148.19</v>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="n">
+      <c r="D2" t="n">
+        <v>120.58</v>
+      </c>
+      <c r="F2" t="n">
         <v>4.4</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" t="n">
         <v>276</v>
       </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/61Weago1KdL._AC_SL1500_.jpg</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Coat Rack; Perfect for Keeping Hats and Coats Off the Floor
 12 Hooks Made of Chrome and Wood in Oak finish
@@ -1330,7 +1325,7 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>{"ASIN": "B003G2ZKRC", "Assembly Instructions Description": "Assembly Required", "Assembly Required": "Yes", "Batteries required": "No", "Best Sellers Rank": "#3,631,965 in Home &amp; Kitchen ( See Top 100 in Home &amp; Kitchen ) #1,223 in Coat Racks", "Brand": "ORE", "Color": "Brown", "Customer Reviews": "4.4 4.4 out of 5 stars 276 ratings 4.4 out of 5 stars", "Finish Type": "Wood", "Finish types": "Wood", "Frame Material": "Wood", "Furniture Finish": "Oak", "Global Trade Identification Number": "00075821458170", "Installation Type": "Free Standing", "Is Discontinued By Manufacturer": "No", "Item Weight": "0.01 Ounces", "Item model number": "R685OAK", "Load Capacity": "350 Pounds", "Manufacturer": "Ore International", "Material": "Wood", "Maximum Weight Recommendation": "350 Pounds", "Product Dimensions": "19 x 73 x 19 inches", "Recommended Uses For Product": "Coats", "Special Feature": "Elegant design", "Style": "Casual,Classic,Elegant", "UPC": "075821458170 882726288203", "Warranty Description": "60 days."}</t>
+          <t>{"ASIN": "B003G2ZKRC", "Assembly Instructions Description": "Assembly Required", "Assembly Required": "Yes", "Batteries required": "No", "Best Sellers Rank": "#4,029,244 in Home &amp; Kitchen ( See Top 100 in Home &amp; Kitchen ) #1,304 in Coat Racks", "Brand": "ORE", "Color": "Brown", "Customer Reviews": "4.4 4.4 out of 5 stars (276) 4.4 out of 5 stars", "Finish Type": "Wood", "Finish types": "Wood", "Frame Material": "Wood", "Furniture Finish": "Oak", "Global Trade Identification Number": "00075821458170", "Installation Type": "Free Standing", "Is Discontinued By Manufacturer": "No", "Item Weight": "0.01 Ounces", "Item model number": "R685OAK", "Load Capacity": "350 Pounds", "Manufacturer": "Ore International", "Material": "Wood", "Maximum Weight Recommendation": "350 Pounds", "Product Dimensions": "19 x 73 x 19 inches", "Recommended Uses For Product": "Coats", "Special Feature": "Elegant design", "Style": "Casual,Classic,Elegant", "UPC": "075821458170 882726288203", "Warranty Description": "60 days."}</t>
         </is>
       </c>
     </row>
@@ -1345,33 +1340,33 @@
           <t>B07SHFPD8S</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>Pipishell Full Motion TV Wall Mount for Echo Show 21/15 and 13-42 Inch Flat Curved Screen TVs &amp; Monitors, Max VESA 200x200mm up to 44lbs, TV Mount Wall Bracket with Rotation Swivel Tilt Extension</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>121</v>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pipishell Full Motion TV Wall Mount for Echo Show 21/15 and 13-43 Inch Flat Curved Screen TVs &amp; Monitors, Max VESA 200x200mm up to 44lbs, TV Mount Wall Bracket with Rotation Swivel Tilt Extension</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" t="n">
         <v>4.6</v>
       </c>
-      <c r="G3" s="0" t="n">
-        <v>133273</v>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61EBlj11AbL._AC_SL1500_.jpg</t>
-        </is>
-      </c>
-      <c r="I3" s="0" t="inlineStr">
-        <is>
-          <t>TV Mount Compatibility - The swivel TV wall mount is compatible with most LED LCD flat or curved 13″-42″ TVs/Monitors up to 44 lbs with VESA mounting patterns 75x75 to 200x200mm. The single TV mount can be installed on single wood studs, concrete, or brick walls, perfectly compatible with SAMSUNG, SONY, LG, VIZIO, TCL, ELEMENT, SCEPTRE, HISENSE and other TV brands. Please confirm your screen size and TV/monitor VESA before ordering.
+      <c r="G3" t="n">
+        <v>146445</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61tI8ajZYZL._AC_SL1499_.jpg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TV Mount Compatibility - The swivel TV wall mount is compatible with most LED LCD flat or curved 13″-43″ TVs/Monitors up to 44 lbs with VESA mounting patterns 75x75 to 200x200mm. The single TV mount can be installed on single wood studs, concrete, or brick walls, perfectly compatible with SAMSUNG, SONY, LG, VIZIO, TCL, ELEMENT, SCEPTRE, HISENSE and other TV brands. Please confirm your screen size and TV/monitor VESA before ordering.
 Full Motion for Optimal Viewing - Our articulating arm mount tilts +9°/-11° for anti-glaring, max swivels 90° display left or right according to your seats position (note: max. swivel angle depends on screen size) and rotates 360° for landscape and portrait orientation. It extends 14.59" and retracts back to 2.7" to save space. Makes your viewing or working feel more enjoyable!
 Universal Monitor Wall Mount - ideal for large computer monitors, especially monitors sizes 13, 17, 19, 21, 24, 27, 32, 34, 35 inch ultrawide monitors with VESA patterns from 75x75mm to 200x200mm. Use it as a full motion monitor wall mount to clear up desktop space and for ergonomic computer screen installation to improve your posture.
 Easy Installation - step-by-step instructions and all the necessary hardware is provided, single stud installation simplifies the placement of the TV/monitor on the wall. Removable TV plate designed for single-person installation which helps you to install this TV wall mount without any hassle.
@@ -1380,7 +1375,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>{"ASIN": "B07SHFPD8S", "Best Sellers Rank": "#89 in Electronics ( See Top 100 in Electronics ) #4 in TV Wall &amp; Ceiling Mounts", "Brand Name": "‎Pipishell", "Color Name": "‎Black", "Customer Reviews": "4.6 4.6 out of 5 stars 133,273 ratings 4.6 out of 5 stars", "Date First Available": "May 31, 2019", "Item Weight": "‎2.7 pounds", "Item model number": "‎PISF1", "Product Dimensions": "‎9.61 x 6.22 x 2.4 inches", "Special Features": "‎Articulating/Full motion/swivel/tilt/wider rotation/low profile/extension"}</t>
+          <t>{"ASIN": "B07SHFPD8S", "Best Sellers Rank": "#67 in Electronics ( See Top 100 in Electronics ) #2 in TV Wall &amp; Ceiling Mounts", "Brand Name": "‎Pipishell", "Color Name": "‎Black Mount without LED", "Customer Reviews": "4.6 4.6 out of 5 stars (146,445) 4.6 out of 5 stars", "Date First Available": "May 31, 2019", "Item Weight": "‎2.83 pounds", "Item model number": "‎PISF1", "Product Dimensions": "‎9.61 x 6.22 x 2.4 inches"}</t>
         </is>
       </c>
     </row>
